--- a/data/trans_camb/P1801_2016_2023-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1801_2016_2023-Habitat-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,32</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-4,74</t>
+          <t>-5,24</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,13</t>
+          <t>-1,84</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 8,1</t>
+          <t>-4,15; 7,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 0,3</t>
+          <t>-9,83; -0,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 2,94</t>
+          <t>-5,8; 1,9</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-7,74%</t>
+          <t>-8,56%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-2,04%</t>
+          <t>-3,32%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 17,03</t>
+          <t>-8,09; 15,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 0,57</t>
+          <t>-15,44; -0,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 5,5</t>
+          <t>-10,01; 3,55</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>16,11</t>
+          <t>4,16</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,19</t>
+          <t>1,89</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9,21</t>
+          <t>3,02</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,51; 36,92</t>
+          <t>-0,21; 8,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 6,34</t>
+          <t>-2,47; 5,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 22,89</t>
+          <t>-0,16; 6,41</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,89; 87,18</t>
+          <t>-0,05; 21,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 11,98</t>
+          <t>-4,08; 10,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,28; 46,06</t>
+          <t>-0,32; 13,16</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-5,57</t>
+          <t>-6,13</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-2,13</t>
+          <t>-10,7</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,78</t>
+          <t>-8,51</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,2; -0,09</t>
+          <t>-11,88; -0,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 18,92</t>
+          <t>-15,36; -5,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 14,25</t>
+          <t>-12,31; -5,06</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-12,02%</t>
+          <t>-13,22%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-3,57%</t>
+          <t>-17,9%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-5,24%</t>
+          <t>-16,0%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-22,86; -0,02</t>
+          <t>-24,11; -1,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 31,8</t>
+          <t>-24,65; -10,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-21,68; 28,44</t>
+          <t>-22,34; -9,94</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>6,06</t>
+          <t>4,65</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,54</t>
+          <t>5,36</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,25</t>
+          <t>5,04</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 10,66</t>
+          <t>-0,22; 9,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 8,36</t>
+          <t>1,19; 9,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 7,72</t>
+          <t>1,74; 8,49</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,77; 24,25</t>
+          <t>-0,47; 20,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,52; 16,13</t>
+          <t>2,18; 18,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 15,74</t>
+          <t>3,44; 17,56</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>6,34</t>
+          <t>1,42</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>-1,2</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,11</t>
+          <t>0,1</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,83; 17,56</t>
+          <t>-1,28; 4,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 8,18</t>
+          <t>-3,51; 1,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 9,28</t>
+          <t>-1,6; 1,76</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-0,02%</t>
+          <t>-2,11%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3,85; 36,71</t>
+          <t>-2,61; 9,01</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 14,48</t>
+          <t>-5,98; 2,03</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 18,12</t>
+          <t>-3,04; 3,45</t>
         </is>
       </c>
     </row>
